--- a/ket_qua_ML.xlsx
+++ b/ket_qua_ML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ML Pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661BA32C-8EC7-4DFD-AF63-3843D538C99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664A0CA6-6A39-4456-8C87-7AF29558A559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="38">
   <si>
     <t>cif_tk_so_nv_phat_sinh</t>
   </si>
@@ -116,918 +116,6 @@
   </si>
   <si>
     <t>Tên ĐVKD</t>
-  </si>
-  <si>
-    <t>002_Chi nhánh Phú Nhuận</t>
-  </si>
-  <si>
-    <t>003_Chi nhánh Lãnh Binh Thăng</t>
-  </si>
-  <si>
-    <t>004_Chi nhánh Nguyễn Trãi</t>
-  </si>
-  <si>
-    <t>006_Chi nhánh Cộng Hòa</t>
-  </si>
-  <si>
-    <t>007_Chi nhánh Cần Thơ</t>
-  </si>
-  <si>
-    <t>008_HDBank Thành phố Thủ Đức</t>
-  </si>
-  <si>
-    <t>009_Chi nhánh Hà Nội</t>
-  </si>
-  <si>
-    <t>010_Chi nhánh Bình Dương</t>
-  </si>
-  <si>
-    <t>011_Chi nhánh TP. Hồ Chí Minh</t>
-  </si>
-  <si>
-    <t>012_HDBank Tây Sài Gòn</t>
-  </si>
-  <si>
-    <t>013_Chi nhánh Ba Đình</t>
-  </si>
-  <si>
-    <t>014_Phòng giao dịch Nguyễn Oanh</t>
-  </si>
-  <si>
-    <t>015_HDBank Bình Thạnh</t>
-  </si>
-  <si>
-    <t>016_Phòng giao dịch Đầm Sen</t>
-  </si>
-  <si>
-    <t>019_Chi nhánh Long An</t>
-  </si>
-  <si>
-    <t>020_Chi nhánh Hoàn Kiếm</t>
-  </si>
-  <si>
-    <t>021_HDBank Đống Đa</t>
-  </si>
-  <si>
-    <t>023_HDBank Ngô Gia Tự</t>
-  </si>
-  <si>
-    <t>024_HDBank Hai Bà Trưng</t>
-  </si>
-  <si>
-    <t>025_Chi nhánh Đà Nẵng</t>
-  </si>
-  <si>
-    <t>026_Phòng giao dịch Lê Duẩn</t>
-  </si>
-  <si>
-    <t>027_Phòng giao dịch Tây Đô</t>
-  </si>
-  <si>
-    <t>028_Phòng giao dịch Hà Đông</t>
-  </si>
-  <si>
-    <t>029_Phòng giao dịch Lạc Long Quân</t>
-  </si>
-  <si>
-    <t>030_Phòng giao dịch Phú Mỹ Hưng</t>
-  </si>
-  <si>
-    <t>031_HDBank Duy Tân</t>
-  </si>
-  <si>
-    <t>033_Phòng giao dịch Hồng Hà</t>
-  </si>
-  <si>
-    <t>036_Phòng giao dịch Hiệp Thành</t>
-  </si>
-  <si>
-    <t>037_Phòng giao dịch Hải Châu</t>
-  </si>
-  <si>
-    <t>038_Phòng giao dịch Nguyễn Duy Trinh</t>
-  </si>
-  <si>
-    <t>040_Chi nhánh Đồng Nai</t>
-  </si>
-  <si>
-    <t>041_Phòng giao dịch Linh Đông</t>
-  </si>
-  <si>
-    <t>042_HDBank Linh Đàm</t>
-  </si>
-  <si>
-    <t>043_Phòng giao dịch Dĩ An</t>
-  </si>
-  <si>
-    <t>044_Chi nhánh Nha Trang</t>
-  </si>
-  <si>
-    <t>046_Chi nhánh An Giang</t>
-  </si>
-  <si>
-    <t>047_Chi nhánh Nghệ An</t>
-  </si>
-  <si>
-    <t>048_Phòng giao dịch Hòa Cường</t>
-  </si>
-  <si>
-    <t>050_Phòng giao dịch Thốt Nốt</t>
-  </si>
-  <si>
-    <t>051_Chi nhánh Vũng Tàu</t>
-  </si>
-  <si>
-    <t>052_HDBank Nam Kỳ Khởi Nghĩa</t>
-  </si>
-  <si>
-    <t>053_HDBank Nguyễn Sơn</t>
-  </si>
-  <si>
-    <t>054_Phòng giao dịch Hòa Hưng</t>
-  </si>
-  <si>
-    <t>055_Phòng giao dịch Tân Phú</t>
-  </si>
-  <si>
-    <t>056_HDBank Nguyễn Hữu Thọ</t>
-  </si>
-  <si>
-    <t>057_HDBank Trần Hưng Đạo</t>
-  </si>
-  <si>
-    <t>058_HDBank Phan Đình Phùng</t>
-  </si>
-  <si>
-    <t>059_HDBank Đông Sài Gòn</t>
-  </si>
-  <si>
-    <t>060_Phòng giao dịch Phan Văn Trị</t>
-  </si>
-  <si>
-    <t>062_HDBank Tây Hồ</t>
-  </si>
-  <si>
-    <t>063_Phòng giao dịch Nguyễn Văn Linh</t>
-  </si>
-  <si>
-    <t>064_Phòng giao dịch Âu Cơ</t>
-  </si>
-  <si>
-    <t>066_HDBank Thủ Đô</t>
-  </si>
-  <si>
-    <t>068_TRUNG TÂM KINH DOANH</t>
-  </si>
-  <si>
-    <t>069_Phòng giao dịch Đông Anh</t>
-  </si>
-  <si>
-    <t>070_Phòng giao dịch Văn Quán</t>
-  </si>
-  <si>
-    <t>072_Phòng giao dịch Lê Thanh Nghị</t>
-  </si>
-  <si>
-    <t>073_Phòng giao dịch Cầu Giấy</t>
-  </si>
-  <si>
-    <t>074_Phòng giao dịch Huỳnh Tấn Phát</t>
-  </si>
-  <si>
-    <t>075_Phòng giao dịch Hà Thành</t>
-  </si>
-  <si>
-    <t>076_Phòng giao dịch Thái Sơn</t>
-  </si>
-  <si>
-    <t>078_Phòng giao dịch Lý Thường Kiệt</t>
-  </si>
-  <si>
-    <t>079_Phòng giao dịch Khu Công Nghiệp AMATA</t>
-  </si>
-  <si>
-    <t>080_Phòng giao dịch Thanh Đa</t>
-  </si>
-  <si>
-    <t>081_Phòng giao dịch Lê Quang Định</t>
-  </si>
-  <si>
-    <t>082_Phòng giao dịch Minh Phụng</t>
-  </si>
-  <si>
-    <t>083_Phòng giao dịch Phước Long</t>
-  </si>
-  <si>
-    <t>084_Phòng giao dịch Thanh Bình</t>
-  </si>
-  <si>
-    <t>085_Phòng giao dịch Khánh Hội</t>
-  </si>
-  <si>
-    <t>086_Phòng giao dịch Nguyễn Văn Quá</t>
-  </si>
-  <si>
-    <t>087_Phòng giao dịch Lê Trọng Tấn</t>
-  </si>
-  <si>
-    <t>088_HDBank Nam Sài Gòn</t>
-  </si>
-  <si>
-    <t>089_Phòng giao dịch Nguyễn Ảnh Thủ</t>
-  </si>
-  <si>
-    <t>090_Phòng giao dịch Nguyễn Văn Cừ</t>
-  </si>
-  <si>
-    <t>092_Phòng giao dịch Thảo Điền</t>
-  </si>
-  <si>
-    <t>093_Phòng giao dịch Bà Rịa</t>
-  </si>
-  <si>
-    <t>096_HDBank Nam Đô</t>
-  </si>
-  <si>
-    <t>097_Phòng giao dịch Kinh Đô</t>
-  </si>
-  <si>
-    <t>098_Phòng giao dịch Chợ Mới</t>
-  </si>
-  <si>
-    <t>101_Phòng giao dịch Triều Khúc</t>
-  </si>
-  <si>
-    <t>102_Phòng giao dịch Kim Liên</t>
-  </si>
-  <si>
-    <t>106_HDBank ĐTBL Châu Đức</t>
-  </si>
-  <si>
-    <t>107_Phòng giao dịch Thanh Xuân</t>
-  </si>
-  <si>
-    <t>108_HDBank Tây Hà Nội</t>
-  </si>
-  <si>
-    <t>109_Phòng giao dịch Quán Hành</t>
-  </si>
-  <si>
-    <t>110_Phòng giao dịch Cam Ranh</t>
-  </si>
-  <si>
-    <t>111_Chi nhánh ĐăkLăk</t>
-  </si>
-  <si>
-    <t>112_Chi nhánh Bắc Ninh</t>
-  </si>
-  <si>
-    <t>113_Phòng giao dịch Long Biên</t>
-  </si>
-  <si>
-    <t>114_Phòng giao dịch Trung Yên</t>
-  </si>
-  <si>
-    <t>116_Phòng giao dịch Thượng Đình</t>
-  </si>
-  <si>
-    <t>117_Phòng giao dịch Mỹ Đình 1</t>
-  </si>
-  <si>
-    <t>118_Phòng giao dịch Mỹ Đình 2</t>
-  </si>
-  <si>
-    <t>121_Chi nhánh Tây Ninh</t>
-  </si>
-  <si>
-    <t>123_Chi nhánh Cà Mau</t>
-  </si>
-  <si>
-    <t>130_Phòng giao dịch Nam Hà Nội</t>
-  </si>
-  <si>
-    <t>131_HDBank ĐTBL HDBank Cư Kuin</t>
-  </si>
-  <si>
-    <t>132_Chi nhánh Hà Tĩnh</t>
-  </si>
-  <si>
-    <t>133_Phòng giao dịch Phước Bình</t>
-  </si>
-  <si>
-    <t>135_Chi nhánh Sở giao dịch Đồng Nai</t>
-  </si>
-  <si>
-    <t>136_Phòng giao dịch Quyết Thắng</t>
-  </si>
-  <si>
-    <t>137_Phòng giao dịch Bửu Long</t>
-  </si>
-  <si>
-    <t>138_Phòng giao dịch Tân Phong</t>
-  </si>
-  <si>
-    <t>139_HDBank ĐTBL Tân Mai</t>
-  </si>
-  <si>
-    <t>140_HDBank Quang Vinh</t>
-  </si>
-  <si>
-    <t>141_Phòng giao dịch Bình Sơn</t>
-  </si>
-  <si>
-    <t>142_HDBank Hố Nai</t>
-  </si>
-  <si>
-    <t>143_Phòng giao dịch Thạnh Phú</t>
-  </si>
-  <si>
-    <t>144_Phòng giao dịch Tân Hiệp</t>
-  </si>
-  <si>
-    <t>145_Phòng giao dịch Tân Hòa</t>
-  </si>
-  <si>
-    <t>146_HDBank ĐTBL Vĩnh An</t>
-  </si>
-  <si>
-    <t>147_HDBank Tam Hiệp</t>
-  </si>
-  <si>
-    <t>148_HDBank Tam Phước</t>
-  </si>
-  <si>
-    <t>149_HDBank ĐTBL Long Bình</t>
-  </si>
-  <si>
-    <t>151_HDBank ĐTBL Long Thành</t>
-  </si>
-  <si>
-    <t>152_HDBank Long Khánh</t>
-  </si>
-  <si>
-    <t>153_HDBank ĐTBL Định Quán</t>
-  </si>
-  <si>
-    <t>154_HDBank ĐTBL Phương Lâm</t>
-  </si>
-  <si>
-    <t>155_HDBank Gia Ray</t>
-  </si>
-  <si>
-    <t>157_HDBank ĐTBL Sông Ray</t>
-  </si>
-  <si>
-    <t>158_HDBank ĐTBL Xuân An</t>
-  </si>
-  <si>
-    <t>159_HDBank Trảng Bom</t>
-  </si>
-  <si>
-    <t>160_HDBank ĐTBL Đông Hòa</t>
-  </si>
-  <si>
-    <t>161_Phòng giao dịch Hố Nai 3</t>
-  </si>
-  <si>
-    <t>162_HDBank Thủ Dầu Một</t>
-  </si>
-  <si>
-    <t>163_Phòng giao dịch Bình An</t>
-  </si>
-  <si>
-    <t>164_Phòng giao dịch Bàu Bàng</t>
-  </si>
-  <si>
-    <t>165_Phòng giao dịch Lái Thiêu</t>
-  </si>
-  <si>
-    <t>167_HDBank Rạch Dừa</t>
-  </si>
-  <si>
-    <t>168_Chi nhánh Nguyễn Đình Chiểu</t>
-  </si>
-  <si>
-    <t>169_Chi nhánh Hàng Xanh</t>
-  </si>
-  <si>
-    <t>170_Chi nhánh Gia Lai</t>
-  </si>
-  <si>
-    <t>171_Chi nhánh Bình Thuận</t>
-  </si>
-  <si>
-    <t>172_Chi nhánh Gia Định</t>
-  </si>
-  <si>
-    <t>173_Phòng giao dịch Khu Nam</t>
-  </si>
-  <si>
-    <t>175_HDBank Chợ Lớn</t>
-  </si>
-  <si>
-    <t>176_HDBank Củ Chi</t>
-  </si>
-  <si>
-    <t>177_Phòng giao dịch Tân Bình</t>
-  </si>
-  <si>
-    <t>180_Phòng giao dịch Nguyễn Thị Định</t>
-  </si>
-  <si>
-    <t>181_Phòng giao dịch Hoàng Diệu</t>
-  </si>
-  <si>
-    <t>182_Phòng giao dịch Trương Định</t>
-  </si>
-  <si>
-    <t>184_Phòng giao dịch Bình Thọ</t>
-  </si>
-  <si>
-    <t>185_Phòng giao dịch Trường Sơn</t>
-  </si>
-  <si>
-    <t>186_Chi nhánh Hùng Vương</t>
-  </si>
-  <si>
-    <t>187_Phòng giao dịch Bắc An Khánh</t>
-  </si>
-  <si>
-    <t>190_Phòng giao dịch Hạ Đình</t>
-  </si>
-  <si>
-    <t>191_Phòng giao dịch Quang Trung</t>
-  </si>
-  <si>
-    <t>192_Phòng giao dịch Mỹ Đình</t>
-  </si>
-  <si>
-    <t>193_Chi nhánh Hồ Gươm</t>
-  </si>
-  <si>
-    <t>195_Phòng giao dịch Vĩnh Tuy</t>
-  </si>
-  <si>
-    <t>197_Phòng giao dịch Yên Phụ</t>
-  </si>
-  <si>
-    <t>198_Phòng giao dịch Sài Đồng</t>
-  </si>
-  <si>
-    <t>201_Phòng giao dịch Đan Phượng</t>
-  </si>
-  <si>
-    <t>202_Phòng giao dịch Thái Thịnh</t>
-  </si>
-  <si>
-    <t>203_HDBank Hải Đăng</t>
-  </si>
-  <si>
-    <t>204_Phòng giao dịch Vinh</t>
-  </si>
-  <si>
-    <t>206_Chi nhánh Quảng Ninh</t>
-  </si>
-  <si>
-    <t>207_Chi nhánh Sóc Trăng</t>
-  </si>
-  <si>
-    <t>208_Phòng giao dịch Vũng Áng</t>
-  </si>
-  <si>
-    <t>209_Phòng giao dịch Châu Đốc</t>
-  </si>
-  <si>
-    <t>210_Phòng giao dịch Châu Phú</t>
-  </si>
-  <si>
-    <t>213_Chi nhánh Vĩnh Long</t>
-  </si>
-  <si>
-    <t>214_Chi nhánh Lâm Đồng</t>
-  </si>
-  <si>
-    <t>215_Chi nhánh Đồng Tháp</t>
-  </si>
-  <si>
-    <t>216_Chi nhánh Kiên Giang</t>
-  </si>
-  <si>
-    <t>217_Chi nhánh Huế</t>
-  </si>
-  <si>
-    <t>218_HDBank ĐTBL Krông Buk</t>
-  </si>
-  <si>
-    <t>219_Phòng giao dịch Ngô Quyền</t>
-  </si>
-  <si>
-    <t>221_Phòng giao dịch Thành Đông</t>
-  </si>
-  <si>
-    <t>222_Phòng giao dịch Điện Biên Phủ</t>
-  </si>
-  <si>
-    <t>223_Phòng giao dịch Trung tâm</t>
-  </si>
-  <si>
-    <t>224_Chi nhánh Thanh Hóa</t>
-  </si>
-  <si>
-    <t>225_Chi nhánh Bến Tre</t>
-  </si>
-  <si>
-    <t>226_Chi nhánh Kon Tum</t>
-  </si>
-  <si>
-    <t>227_Chi nhánh Quảng Ngãi</t>
-  </si>
-  <si>
-    <t>229_Chi nhánh Lạng Sơn</t>
-  </si>
-  <si>
-    <t>230_Chi nhánh Quảng Nam</t>
-  </si>
-  <si>
-    <t>231_Chi nhánh Nam Định</t>
-  </si>
-  <si>
-    <t>232_Chi nhánh Bình Phước</t>
-  </si>
-  <si>
-    <t>235_HDBank ĐTBL Ea H'Leo</t>
-  </si>
-  <si>
-    <t>236_Phòng giao dịch An Nhơn</t>
-  </si>
-  <si>
-    <t>237_Phòng giao dịch Đức Phổ</t>
-  </si>
-  <si>
-    <t>238_Phòng giao dịch Bình Điền</t>
-  </si>
-  <si>
-    <t>239_Phòng giao dịch Bắc Sông Hương</t>
-  </si>
-  <si>
-    <t>241_Phòng giao dịch Châu Thành</t>
-  </si>
-  <si>
-    <t>242_Phòng giao dịch Sa Đéc</t>
-  </si>
-  <si>
-    <t>244_HDBank Cẩm Phả</t>
-  </si>
-  <si>
-    <t>245_Phòng giao dịch Mạo Khê</t>
-  </si>
-  <si>
-    <t>246_Phòng giao dịch Đồng Đăng</t>
-  </si>
-  <si>
-    <t>247_Chi nhánh Bắc Giang</t>
-  </si>
-  <si>
-    <t>249_Chi nhánh Ninh Bình</t>
-  </si>
-  <si>
-    <t>250_Chi nhánh Phú Yên</t>
-  </si>
-  <si>
-    <t>251_Chi nhánh Quảng Bình</t>
-  </si>
-  <si>
-    <t>252_Chi nhánh Phú Quốc</t>
-  </si>
-  <si>
-    <t>253_Phòng giao dịch An Khê</t>
-  </si>
-  <si>
-    <t>254_Chi nhánh Tiền Giang</t>
-  </si>
-  <si>
-    <t>255_Phòng giao dịch Tầm Vu</t>
-  </si>
-  <si>
-    <t>256_Phòng giao dịch Ba Tri</t>
-  </si>
-  <si>
-    <t>257_Phòng giao dịch Vũng Liêm</t>
-  </si>
-  <si>
-    <t>258_Phòng giao dịch Thoại Sơn</t>
-  </si>
-  <si>
-    <t>260_Phòng giao dịch Trần Đề</t>
-  </si>
-  <si>
-    <t>262_Phòng giao dịch Năm Căn</t>
-  </si>
-  <si>
-    <t>264_Phòng giao dịch Mỏ Cày Bắc</t>
-  </si>
-  <si>
-    <t>265_Phòng giao dịch Tam Bình</t>
-  </si>
-  <si>
-    <t>266_Phòng giao dịch Hồng Ngự</t>
-  </si>
-  <si>
-    <t>267_Phòng giao dịch Ngã Năm</t>
-  </si>
-  <si>
-    <t>269_Phòng giao dịch Tắc Vân</t>
-  </si>
-  <si>
-    <t>270_Phòng giao dịch Đức Trọng</t>
-  </si>
-  <si>
-    <t>271_Phòng giao dịch Đăk Đoa</t>
-  </si>
-  <si>
-    <t>273_Phòng giao dịch Ngọc Hồi</t>
-  </si>
-  <si>
-    <t>274_Phòng giao dịch Tam Kỳ</t>
-  </si>
-  <si>
-    <t>275_Phòng giao dịch Hàm Thuận Nam</t>
-  </si>
-  <si>
-    <t>277_Phòng giao dịch Đức Linh</t>
-  </si>
-  <si>
-    <t>280_Phòng giao dịch Yên Phong</t>
-  </si>
-  <si>
-    <t>282_Phòng giao dịch Chợ Rồng</t>
-  </si>
-  <si>
-    <t>283_Phòng giao dịch Tây Sơn</t>
-  </si>
-  <si>
-    <t>284_Chi nhánh Thái Nguyên</t>
-  </si>
-  <si>
-    <t>286_Phòng giao dịch Lộc Hà</t>
-  </si>
-  <si>
-    <t>287_Phòng giao dịch Hương Sơn</t>
-  </si>
-  <si>
-    <t>288_Phòng giao dịch Tĩnh Gia</t>
-  </si>
-  <si>
-    <t>289_Phòng giao dịch Tân Châu</t>
-  </si>
-  <si>
-    <t>290_Phòng giao dịch Uông Bí</t>
-  </si>
-  <si>
-    <t>293_Phòng giao dịch Hương Thủy</t>
-  </si>
-  <si>
-    <t>295_Phòng giao dịch Hữu Lũng</t>
-  </si>
-  <si>
-    <t>296_Phòng giao dịch Bồng Sơn</t>
-  </si>
-  <si>
-    <t>297_Chi nhánh Đăk Nông</t>
-  </si>
-  <si>
-    <t>298_Chi nhánh Vĩnh Phúc</t>
-  </si>
-  <si>
-    <t>299_Chi nhánh Hưng Yên</t>
-  </si>
-  <si>
-    <t>300_Phòng giao dịch Duy Minh</t>
-  </si>
-  <si>
-    <t>301_Phòng giao dịch Gò Công</t>
-  </si>
-  <si>
-    <t>302_Phòng giao dịch Bù Đăng</t>
-  </si>
-  <si>
-    <t>303_Phòng giao dịch Hòa Hiệp</t>
-  </si>
-  <si>
-    <t>304_Chi nhánh Phú Thọ</t>
-  </si>
-  <si>
-    <t>305_Phòng giao dịch Bình Minh</t>
-  </si>
-  <si>
-    <t>306_Phòng giao dịch Phan Rí</t>
-  </si>
-  <si>
-    <t>307_Phòng giao dịch Thuận Thành</t>
-  </si>
-  <si>
-    <t>309_Chi nhánh Sơn La</t>
-  </si>
-  <si>
-    <t>311_Phòng giao dịch Chơn Thành</t>
-  </si>
-  <si>
-    <t>312_Phòng giao dịch Di Linh</t>
-  </si>
-  <si>
-    <t>313_Phòng giao dịch Việt Yên</t>
-  </si>
-  <si>
-    <t>314_Phòng giao dịch Ba Đồn</t>
-  </si>
-  <si>
-    <t>315_Chi nhánh Ninh Thuận</t>
-  </si>
-  <si>
-    <t>316_Chi nhánh Hà Nam</t>
-  </si>
-  <si>
-    <t>318_Phòng giao dịch Tuy An</t>
-  </si>
-  <si>
-    <t>319_Phòng giao dịch Hương Trà</t>
-  </si>
-  <si>
-    <t>320_Phòng giao dịch Điện Bàn</t>
-  </si>
-  <si>
-    <t>321_Phòng giao dịch Châu Ổ</t>
-  </si>
-  <si>
-    <t>325_Phòng giao dịch Đắk Hà</t>
-  </si>
-  <si>
-    <t>327_Phòng giao dịch Tân Yên</t>
-  </si>
-  <si>
-    <t>328_Phòng giao dịch Đăk Mil</t>
-  </si>
-  <si>
-    <t>329_Phòng giao dịch Khoái Châu</t>
-  </si>
-  <si>
-    <t>330_Phòng giao dịch Bố Trạch</t>
-  </si>
-  <si>
-    <t>331_Phòng giao dịch Thành Nam</t>
-  </si>
-  <si>
-    <t>332_Phòng giao dịch Sông Hinh</t>
-  </si>
-  <si>
-    <t>333_Phòng giao dịch Kiến Đức</t>
-  </si>
-  <si>
-    <t>334_Phòng giao dịch Tư Nghĩa</t>
-  </si>
-  <si>
-    <t>335_Phòng giao dịch Núi Thành</t>
-  </si>
-  <si>
-    <t>336_Phòng giao dịch Lệ Thủy</t>
-  </si>
-  <si>
-    <t>337_Phòng giao dịch Phổ Yên</t>
-  </si>
-  <si>
-    <t>338_Chi nhánh Yên Bái</t>
-  </si>
-  <si>
-    <t>339_Phòng giao dịch Cai Lậy</t>
-  </si>
-  <si>
-    <t>340_Chi nhánh Trà Vinh</t>
-  </si>
-  <si>
-    <t>341_Chi nhánh Cao Bằng</t>
-  </si>
-  <si>
-    <t>343_Chi nhánh Tuyên Quang</t>
-  </si>
-  <si>
-    <t>346_Chi nhánh Hòa Bình</t>
-  </si>
-  <si>
-    <t>347_Phòng giao dịch Giá Rai</t>
-  </si>
-  <si>
-    <t>348_Phòng giao dịch Yên Lạc</t>
-  </si>
-  <si>
-    <t>351_Phòng giao dịch Hòn Đất</t>
-  </si>
-  <si>
-    <t>352_Phòng giao dịch Hải Hậu</t>
-  </si>
-  <si>
-    <t>354_Phòng giao dịch Diêm Điền</t>
-  </si>
-  <si>
-    <t>355_Phòng giao dịch Đắk Bla</t>
-  </si>
-  <si>
-    <t>356_Phòng giao dịch Phúc Yên</t>
-  </si>
-  <si>
-    <t>357_Phòng giao dịch Minh Diệu</t>
-  </si>
-  <si>
-    <t>358_Chi nhánh Hậu Giang</t>
-  </si>
-  <si>
-    <t>359_Chi nhánh Lai Châu</t>
-  </si>
-  <si>
-    <t>360_Phòng giao dịch Ninh Phước</t>
-  </si>
-  <si>
-    <t>361_Phòng giao dịch Lục Nam</t>
-  </si>
-  <si>
-    <t>362_Phòng giao dịch Lập Thạch</t>
-  </si>
-  <si>
-    <t>363_Phòng giao dịch Hoa Lư</t>
-  </si>
-  <si>
-    <t>364_Chi nhánh Điện Biên</t>
-  </si>
-  <si>
-    <t>365_Phòng giao dịch Yên Khánh</t>
-  </si>
-  <si>
-    <t>367_HDBank Hóc Môn</t>
-  </si>
-  <si>
-    <t>376_Chi nhánh Bắc Kạn</t>
-  </si>
-  <si>
-    <t>377_Phòng giao dịch Phú An</t>
-  </si>
-  <si>
-    <t>378_Phòng giao dịch Lý Nhân</t>
-  </si>
-  <si>
-    <t>380_Chi nhánh Tân Uyên</t>
-  </si>
-  <si>
-    <t>387_Phòng giao dịch Phù Yên</t>
-  </si>
-  <si>
-    <t>389_Phòng giao dịch Văn Lâm</t>
-  </si>
-  <si>
-    <t>391_Phòng giao dịch Ninh Sơn</t>
-  </si>
-  <si>
-    <t>392_Phòng giao dịch Ninh Hải</t>
-  </si>
-  <si>
-    <t>393_Phòng giao dịch Gia Viễn</t>
-  </si>
-  <si>
-    <t>394_Phòng giao dịch Thanh Thủy</t>
-  </si>
-  <si>
-    <t>398_Chi nhánh Hà Giang</t>
-  </si>
-  <si>
-    <t>399_Chi nhánh Móng Cái</t>
-  </si>
-  <si>
-    <t>406_Phòng giao dịch Bình Lục</t>
-  </si>
-  <si>
-    <t>407_Chi nhánh Ninh Hòa</t>
-  </si>
-  <si>
-    <t>409_Chi nhánh Tân An</t>
-  </si>
-  <si>
-    <t>412_Chi nhánh Thủy Nguyên</t>
-  </si>
-  <si>
-    <t>415_Phòng giao dịch Duyên Hải</t>
-  </si>
-  <si>
-    <t>419_Phòng giao dịch Ngã Bảy</t>
-  </si>
-  <si>
-    <t>420_Chi nhánh Đông Đắk Lắk</t>
-  </si>
-  <si>
-    <t>424_Phòng giao dịch Đại Từ</t>
-  </si>
-  <si>
-    <t>456_Phòng giao dịch Thành Cổ</t>
-  </si>
-  <si>
-    <t>568_Chi nhánh Mỹ Hào</t>
   </si>
   <si>
     <t>Chi nhánh</t>
@@ -1494,9 +582,6 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
       <c r="B2">
         <v>9</v>
       </c>
@@ -1582,19 +667,16 @@
         <v>4</v>
       </c>
       <c r="AD2" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF2">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
       <c r="B3">
         <v>10</v>
       </c>
@@ -1680,19 +762,16 @@
         <v>2</v>
       </c>
       <c r="AD3" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF3">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
       <c r="B4">
         <v>7.25</v>
       </c>
@@ -1778,19 +857,16 @@
         <v>4</v>
       </c>
       <c r="AD4" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE4" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
       <c r="B5">
         <v>9.5</v>
       </c>
@@ -1876,19 +952,16 @@
         <v>2</v>
       </c>
       <c r="AD5" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF5">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
       <c r="B6">
         <v>9.3333333333333339</v>
       </c>
@@ -1974,19 +1047,16 @@
         <v>3</v>
       </c>
       <c r="AD6" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
       <c r="B7">
         <v>8</v>
       </c>
@@ -2072,19 +1142,16 @@
         <v>2</v>
       </c>
       <c r="AD7" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE7" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF7">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
       <c r="B8">
         <v>7</v>
       </c>
@@ -2170,19 +1237,16 @@
         <v>2</v>
       </c>
       <c r="AD8" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE8" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
       <c r="B9">
         <v>7.5</v>
       </c>
@@ -2268,19 +1332,16 @@
         <v>2</v>
       </c>
       <c r="AD9" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE9" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF9">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>40</v>
-      </c>
       <c r="B10">
         <v>10</v>
       </c>
@@ -2366,19 +1427,16 @@
         <v>2</v>
       </c>
       <c r="AD10" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE10" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF10">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>41</v>
-      </c>
       <c r="B11">
         <v>10</v>
       </c>
@@ -2464,19 +1522,16 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE11" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF11">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>42</v>
-      </c>
       <c r="B12">
         <v>8</v>
       </c>
@@ -2562,19 +1617,16 @@
         <v>3</v>
       </c>
       <c r="AD12" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE12" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF12">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>43</v>
-      </c>
       <c r="B13">
         <v>6</v>
       </c>
@@ -2651,19 +1703,16 @@
         <v>1</v>
       </c>
       <c r="AD13" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE13" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF13">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>44</v>
-      </c>
       <c r="B14">
         <v>10</v>
       </c>
@@ -2749,19 +1798,16 @@
         <v>2</v>
       </c>
       <c r="AD14" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE14" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF14">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
       <c r="B15">
         <v>8</v>
       </c>
@@ -2844,19 +1890,16 @@
         <v>1</v>
       </c>
       <c r="AD15" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE15" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF15">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
       <c r="B16">
         <v>4.666666666666667</v>
       </c>
@@ -2942,19 +1985,16 @@
         <v>3</v>
       </c>
       <c r="AD16" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE16" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
+    <row r="17" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>9.6666666666666661</v>
       </c>
@@ -3040,19 +2080,16 @@
         <v>3</v>
       </c>
       <c r="AD17" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
+    <row r="18" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>2</v>
       </c>
@@ -3120,19 +2157,16 @@
         <v>1</v>
       </c>
       <c r="AD18" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE18" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>49</v>
-      </c>
+    <row r="19" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>10</v>
       </c>
@@ -3218,19 +2252,16 @@
         <v>1</v>
       </c>
       <c r="AD19" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE19" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
+    <row r="20" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>10</v>
       </c>
@@ -3316,19 +2347,16 @@
         <v>2</v>
       </c>
       <c r="AD20" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE20" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>51</v>
-      </c>
+    <row r="21" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>10</v>
       </c>
@@ -3414,19 +2442,16 @@
         <v>1</v>
       </c>
       <c r="AD21" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE21" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>52</v>
-      </c>
+    <row r="22" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>9</v>
       </c>
@@ -3512,19 +2537,16 @@
         <v>1</v>
       </c>
       <c r="AD22" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE22" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>53</v>
-      </c>
+    <row r="23" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>10</v>
       </c>
@@ -3610,19 +2632,16 @@
         <v>1</v>
       </c>
       <c r="AD23" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE23" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>54</v>
-      </c>
+    <row r="24" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>3</v>
       </c>
@@ -3699,19 +2718,16 @@
         <v>1</v>
       </c>
       <c r="AD24" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE24" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
+    <row r="25" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>6</v>
       </c>
@@ -3797,19 +2813,16 @@
         <v>1</v>
       </c>
       <c r="AD25" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE25" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>56</v>
-      </c>
+    <row r="26" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>2</v>
       </c>
@@ -3895,19 +2908,16 @@
         <v>1</v>
       </c>
       <c r="AD26" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE26" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>57</v>
-      </c>
+    <row r="27" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>7.5</v>
       </c>
@@ -3993,19 +3003,16 @@
         <v>2</v>
       </c>
       <c r="AD27" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE27" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>58</v>
-      </c>
+    <row r="28" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>10</v>
       </c>
@@ -4091,19 +3098,16 @@
         <v>1</v>
       </c>
       <c r="AD28" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE28" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>59</v>
-      </c>
+    <row r="29" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>6</v>
       </c>
@@ -4189,19 +3193,16 @@
         <v>1</v>
       </c>
       <c r="AD29" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE29" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>60</v>
-      </c>
+    <row r="30" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>6</v>
       </c>
@@ -4287,19 +3288,16 @@
         <v>1</v>
       </c>
       <c r="AD30" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE30" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>61</v>
-      </c>
+    <row r="31" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>5</v>
       </c>
@@ -4385,19 +3383,16 @@
         <v>1</v>
       </c>
       <c r="AD31" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE31" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>62</v>
-      </c>
+    <row r="32" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>8</v>
       </c>
@@ -4483,19 +3478,16 @@
         <v>2</v>
       </c>
       <c r="AD32" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE32" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>63</v>
-      </c>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>10</v>
       </c>
@@ -4581,19 +3573,16 @@
         <v>2</v>
       </c>
       <c r="AD33" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE33" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>64</v>
-      </c>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>3</v>
       </c>
@@ -4670,19 +3659,16 @@
         <v>1</v>
       </c>
       <c r="AD34" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE34" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>65</v>
-      </c>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>10</v>
       </c>
@@ -4768,19 +3754,16 @@
         <v>1</v>
       </c>
       <c r="AD35" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE35" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>66</v>
-      </c>
+    <row r="36" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>3.666666666666667</v>
       </c>
@@ -4866,19 +3849,16 @@
         <v>3</v>
       </c>
       <c r="AD36" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE36" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>67</v>
-      </c>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>10</v>
       </c>
@@ -4964,19 +3944,16 @@
         <v>1</v>
       </c>
       <c r="AD37" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE37" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>68</v>
-      </c>
+    <row r="38" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>6.5</v>
       </c>
@@ -5062,19 +4039,16 @@
         <v>2</v>
       </c>
       <c r="AD38" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE38" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>69</v>
-      </c>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>2</v>
       </c>
@@ -5151,19 +4125,16 @@
         <v>1</v>
       </c>
       <c r="AD39" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE39" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>70</v>
-      </c>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>3</v>
       </c>
@@ -5249,19 +4220,16 @@
         <v>1</v>
       </c>
       <c r="AD40" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE40" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>71</v>
-      </c>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>6.666666666666667</v>
       </c>
@@ -5347,19 +4315,16 @@
         <v>3</v>
       </c>
       <c r="AD41" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE41" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF41">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>72</v>
-      </c>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>4.5</v>
       </c>
@@ -5445,19 +4410,16 @@
         <v>2</v>
       </c>
       <c r="AD42" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE42" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF42">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>73</v>
-      </c>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>9.5</v>
       </c>
@@ -5543,19 +4505,16 @@
         <v>2</v>
       </c>
       <c r="AD43" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE43" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF43">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>74</v>
-      </c>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>5</v>
       </c>
@@ -5632,19 +4591,16 @@
         <v>1</v>
       </c>
       <c r="AD44" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE44" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>75</v>
-      </c>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>5</v>
       </c>
@@ -5721,19 +4677,16 @@
         <v>1</v>
       </c>
       <c r="AD45" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE45" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>76</v>
-      </c>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>5</v>
       </c>
@@ -5810,19 +4763,16 @@
         <v>1</v>
       </c>
       <c r="AD46" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE46" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>77</v>
-      </c>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>7</v>
       </c>
@@ -5908,19 +4858,16 @@
         <v>2</v>
       </c>
       <c r="AD47" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE47" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>78</v>
-      </c>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>10</v>
       </c>
@@ -6006,19 +4953,16 @@
         <v>1</v>
       </c>
       <c r="AD48" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE48" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF48">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>79</v>
-      </c>
+    <row r="49" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>10</v>
       </c>
@@ -6104,19 +5048,16 @@
         <v>1</v>
       </c>
       <c r="AD49" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE49" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF49">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>80</v>
-      </c>
+    <row r="50" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>3</v>
       </c>
@@ -6184,19 +5125,16 @@
         <v>1</v>
       </c>
       <c r="AD50" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE50" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>81</v>
-      </c>
+    <row r="51" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>9.5</v>
       </c>
@@ -6282,19 +5220,16 @@
         <v>2</v>
       </c>
       <c r="AD51" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE51" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF51">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>82</v>
-      </c>
+    <row r="52" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>3</v>
       </c>
@@ -6371,19 +5306,16 @@
         <v>1</v>
       </c>
       <c r="AD52" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE52" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>83</v>
-      </c>
+    <row r="53" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>10</v>
       </c>
@@ -6469,19 +5401,16 @@
         <v>1</v>
       </c>
       <c r="AD53" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE53" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF53">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>84</v>
-      </c>
+    <row r="54" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>10</v>
       </c>
@@ -6567,19 +5496,16 @@
         <v>2</v>
       </c>
       <c r="AD54" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE54" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF54">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>85</v>
-      </c>
+    <row r="55" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>5</v>
       </c>
@@ -6665,19 +5591,16 @@
         <v>2</v>
       </c>
       <c r="AD55" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE55" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF55">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>86</v>
-      </c>
+    <row r="56" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>10</v>
       </c>
@@ -6763,19 +5686,16 @@
         <v>1</v>
       </c>
       <c r="AD56" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE56" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>87</v>
-      </c>
+    <row r="57" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>6</v>
       </c>
@@ -6840,19 +5760,16 @@
         <v>1</v>
       </c>
       <c r="AD57" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE57" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>88</v>
-      </c>
+    <row r="58" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>4</v>
       </c>
@@ -6929,19 +5846,16 @@
         <v>1</v>
       </c>
       <c r="AD58" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE58" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>89</v>
-      </c>
+    <row r="59" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>7</v>
       </c>
@@ -7027,19 +5941,16 @@
         <v>1</v>
       </c>
       <c r="AD59" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE59" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>90</v>
-      </c>
+    <row r="60" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>4</v>
       </c>
@@ -7107,19 +6018,16 @@
         <v>1</v>
       </c>
       <c r="AD60" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE60" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>91</v>
-      </c>
+    <row r="61" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>10</v>
       </c>
@@ -7205,19 +6113,16 @@
         <v>1</v>
       </c>
       <c r="AD61" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE61" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF61">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>92</v>
-      </c>
+    <row r="62" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>6</v>
       </c>
@@ -7303,19 +6208,16 @@
         <v>1</v>
       </c>
       <c r="AD62" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE62" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF62">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>93</v>
-      </c>
+    <row r="63" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>10</v>
       </c>
@@ -7401,19 +6303,16 @@
         <v>1</v>
       </c>
       <c r="AD63" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE63" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF63">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>94</v>
-      </c>
+    <row r="64" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>5</v>
       </c>
@@ -7499,19 +6398,16 @@
         <v>1</v>
       </c>
       <c r="AD64" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE64" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF64">
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>95</v>
-      </c>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>6</v>
       </c>
@@ -7597,19 +6493,16 @@
         <v>1</v>
       </c>
       <c r="AD65" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE65" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF65">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>96</v>
-      </c>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>2</v>
       </c>
@@ -7677,19 +6570,16 @@
         <v>1</v>
       </c>
       <c r="AD66" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE66" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>97</v>
-      </c>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>5</v>
       </c>
@@ -7775,19 +6665,16 @@
         <v>1</v>
       </c>
       <c r="AD67" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE67" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>98</v>
-      </c>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>10</v>
       </c>
@@ -7873,19 +6760,16 @@
         <v>1</v>
       </c>
       <c r="AD68" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE68" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF68">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>99</v>
-      </c>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>10</v>
       </c>
@@ -7971,19 +6855,16 @@
         <v>1</v>
       </c>
       <c r="AD69" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE69" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>100</v>
-      </c>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>1</v>
       </c>
@@ -8060,19 +6941,16 @@
         <v>1</v>
       </c>
       <c r="AD70" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE70" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>101</v>
-      </c>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>10</v>
       </c>
@@ -8158,19 +7036,16 @@
         <v>1</v>
       </c>
       <c r="AD71" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE71" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>102</v>
-      </c>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>2.5</v>
       </c>
@@ -8256,19 +7131,16 @@
         <v>2</v>
       </c>
       <c r="AD72" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE72" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>103</v>
-      </c>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>6</v>
       </c>
@@ -8354,19 +7226,16 @@
         <v>1</v>
       </c>
       <c r="AD73" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE73" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>104</v>
-      </c>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>10</v>
       </c>
@@ -8452,19 +7321,16 @@
         <v>1</v>
       </c>
       <c r="AD74" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE74" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF74">
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>105</v>
-      </c>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>1</v>
       </c>
@@ -8532,19 +7398,16 @@
         <v>1</v>
       </c>
       <c r="AD75" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE75" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF75">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>106</v>
-      </c>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>6</v>
       </c>
@@ -8630,19 +7493,16 @@
         <v>1</v>
       </c>
       <c r="AD76" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE76" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF76">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>107</v>
-      </c>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>2</v>
       </c>
@@ -8728,19 +7588,16 @@
         <v>1</v>
       </c>
       <c r="AD77" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE77" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF77">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>108</v>
-      </c>
+    <row r="78" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>10</v>
       </c>
@@ -8826,19 +7683,16 @@
         <v>1</v>
       </c>
       <c r="AD78" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE78" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF78">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>109</v>
-      </c>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>10</v>
       </c>
@@ -8906,19 +7760,16 @@
         <v>1</v>
       </c>
       <c r="AD79" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE79" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>110</v>
-      </c>
+    <row r="80" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>2</v>
       </c>
@@ -8986,19 +7837,16 @@
         <v>1</v>
       </c>
       <c r="AD80" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE80" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF80">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>111</v>
-      </c>
+    <row r="81" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>9</v>
       </c>
@@ -9075,19 +7923,16 @@
         <v>1</v>
       </c>
       <c r="AD81" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE81" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF81">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>112</v>
-      </c>
+    <row r="82" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>1</v>
       </c>
@@ -9155,19 +8000,16 @@
         <v>1</v>
       </c>
       <c r="AD82" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE82" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>113</v>
-      </c>
+    <row r="83" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>10</v>
       </c>
@@ -9250,19 +8092,16 @@
         <v>1</v>
       </c>
       <c r="AD83" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE83" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF83">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>114</v>
-      </c>
+    <row r="84" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>9</v>
       </c>
@@ -9348,19 +8187,16 @@
         <v>1</v>
       </c>
       <c r="AD84" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE84" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF84">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>115</v>
-      </c>
+    <row r="85" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>8</v>
       </c>
@@ -9446,19 +8282,16 @@
         <v>2</v>
       </c>
       <c r="AD85" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE85" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF85">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>116</v>
-      </c>
+    <row r="86" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>7</v>
       </c>
@@ -9544,19 +8377,16 @@
         <v>2</v>
       </c>
       <c r="AD86" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE86" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>117</v>
-      </c>
+    <row r="87" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>5</v>
       </c>
@@ -9642,19 +8472,16 @@
         <v>1</v>
       </c>
       <c r="AD87" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE87" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>118</v>
-      </c>
+    <row r="88" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>9.25</v>
       </c>
@@ -9740,19 +8567,16 @@
         <v>4</v>
       </c>
       <c r="AD88" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE88" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF88">
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>119</v>
-      </c>
+    <row r="89" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>10</v>
       </c>
@@ -9838,19 +8662,16 @@
         <v>3</v>
       </c>
       <c r="AD89" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE89" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF89">
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>120</v>
-      </c>
+    <row r="90" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>6</v>
       </c>
@@ -9936,19 +8757,16 @@
         <v>1</v>
       </c>
       <c r="AD90" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE90" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF90">
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>121</v>
-      </c>
+    <row r="91" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>4</v>
       </c>
@@ -10034,19 +8852,16 @@
         <v>1</v>
       </c>
       <c r="AD91" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE91" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF91">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>122</v>
-      </c>
+    <row r="92" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>1</v>
       </c>
@@ -10114,19 +8929,16 @@
         <v>1</v>
       </c>
       <c r="AD92" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE92" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>123</v>
-      </c>
+    <row r="93" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>5</v>
       </c>
@@ -10212,19 +9024,16 @@
         <v>1</v>
       </c>
       <c r="AD93" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE93" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF93">
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>124</v>
-      </c>
+    <row r="94" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>8</v>
       </c>
@@ -10310,19 +9119,16 @@
         <v>1</v>
       </c>
       <c r="AD94" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE94" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF94">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>125</v>
-      </c>
+    <row r="95" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>7.333333333333333</v>
       </c>
@@ -10408,19 +9214,16 @@
         <v>3</v>
       </c>
       <c r="AD95" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE95" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF95">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>126</v>
-      </c>
+    <row r="96" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>10</v>
       </c>
@@ -10506,19 +9309,16 @@
         <v>1</v>
       </c>
       <c r="AD96" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE96" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>127</v>
-      </c>
+    <row r="97" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>10</v>
       </c>
@@ -10598,19 +9398,16 @@
         <v>1</v>
       </c>
       <c r="AD97" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE97" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF97">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>128</v>
-      </c>
+    <row r="98" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>5</v>
       </c>
@@ -10696,19 +9493,16 @@
         <v>3</v>
       </c>
       <c r="AD98" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE98" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF98">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>129</v>
-      </c>
+    <row r="99" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>5</v>
       </c>
@@ -10794,19 +9588,16 @@
         <v>2</v>
       </c>
       <c r="AD99" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE99" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF99">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>130</v>
-      </c>
+    <row r="100" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>10</v>
       </c>
@@ -10892,19 +9683,16 @@
         <v>1</v>
       </c>
       <c r="AD100" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE100" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF100">
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>131</v>
-      </c>
+    <row r="101" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>8.5</v>
       </c>
@@ -10990,19 +9778,16 @@
         <v>6</v>
       </c>
       <c r="AD101" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE101" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>132</v>
-      </c>
+    <row r="102" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>8</v>
       </c>
@@ -11088,19 +9873,16 @@
         <v>2</v>
       </c>
       <c r="AD102" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE102" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF102">
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>133</v>
-      </c>
+    <row r="103" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>10</v>
       </c>
@@ -11186,19 +9968,16 @@
         <v>1</v>
       </c>
       <c r="AD103" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE103" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>134</v>
-      </c>
+    <row r="104" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>5</v>
       </c>
@@ -11284,19 +10063,16 @@
         <v>1</v>
       </c>
       <c r="AD104" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE104" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>135</v>
-      </c>
+    <row r="105" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>10</v>
       </c>
@@ -11382,19 +10158,16 @@
         <v>1</v>
       </c>
       <c r="AD105" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE105" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>136</v>
-      </c>
+    <row r="106" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>10</v>
       </c>
@@ -11480,19 +10253,16 @@
         <v>2</v>
       </c>
       <c r="AD106" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE106" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF106">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>137</v>
-      </c>
+    <row r="107" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>4</v>
       </c>
@@ -11560,19 +10330,16 @@
         <v>1</v>
       </c>
       <c r="AD107" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE107" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF107">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>138</v>
-      </c>
+    <row r="108" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>8</v>
       </c>
@@ -11658,19 +10425,16 @@
         <v>2</v>
       </c>
       <c r="AD108" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE108" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF108">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>139</v>
-      </c>
+    <row r="109" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>0</v>
       </c>
@@ -11741,19 +10505,16 @@
         <v>1</v>
       </c>
       <c r="AD109" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE109" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF109">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>140</v>
-      </c>
+    <row r="110" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>3</v>
       </c>
@@ -11821,19 +10582,16 @@
         <v>1</v>
       </c>
       <c r="AD110" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE110" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF110">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>141</v>
-      </c>
+    <row r="111" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>2</v>
       </c>
@@ -11901,19 +10659,16 @@
         <v>1</v>
       </c>
       <c r="AD111" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE111" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF111">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>142</v>
-      </c>
+    <row r="112" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>2.5</v>
       </c>
@@ -11981,19 +10736,16 @@
         <v>2</v>
       </c>
       <c r="AD112" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE112" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF112">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>143</v>
-      </c>
+    <row r="113" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>4</v>
       </c>
@@ -12079,19 +10831,16 @@
         <v>3</v>
       </c>
       <c r="AD113" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE113" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF113">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>144</v>
-      </c>
+    <row r="114" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>5</v>
       </c>
@@ -12177,19 +10926,16 @@
         <v>2</v>
       </c>
       <c r="AD114" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE114" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF114">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>145</v>
-      </c>
+    <row r="115" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>5</v>
       </c>
@@ -12275,19 +11021,16 @@
         <v>2</v>
       </c>
       <c r="AD115" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE115" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF115">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>146</v>
-      </c>
+    <row r="116" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>10</v>
       </c>
@@ -12373,19 +11116,16 @@
         <v>2</v>
       </c>
       <c r="AD116" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE116" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF116">
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>147</v>
-      </c>
+    <row r="117" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>10</v>
       </c>
@@ -12471,19 +11211,16 @@
         <v>2</v>
       </c>
       <c r="AD117" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE117" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF117">
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>148</v>
-      </c>
+    <row r="118" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>10</v>
       </c>
@@ -12569,19 +11306,16 @@
         <v>3</v>
       </c>
       <c r="AD118" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE118" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF118">
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>149</v>
-      </c>
+    <row r="119" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>3.666666666666667</v>
       </c>
@@ -12667,19 +11401,16 @@
         <v>3</v>
       </c>
       <c r="AD119" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE119" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF119">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>150</v>
-      </c>
+    <row r="120" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>6</v>
       </c>
@@ -12756,19 +11487,16 @@
         <v>4</v>
       </c>
       <c r="AD120" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE120" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF120">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>151</v>
-      </c>
+    <row r="121" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>3</v>
       </c>
@@ -12854,19 +11582,16 @@
         <v>1</v>
       </c>
       <c r="AD121" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE121" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF121">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>152</v>
-      </c>
+    <row r="122" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>6</v>
       </c>
@@ -12952,19 +11677,16 @@
         <v>1</v>
       </c>
       <c r="AD122" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE122" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF122">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>153</v>
-      </c>
+    <row r="123" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>10</v>
       </c>
@@ -13050,19 +11772,16 @@
         <v>3</v>
       </c>
       <c r="AD123" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE123" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF123">
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>154</v>
-      </c>
+    <row r="124" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>3.5</v>
       </c>
@@ -13139,19 +11858,16 @@
         <v>2</v>
       </c>
       <c r="AD124" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE124" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF124">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>155</v>
-      </c>
+    <row r="125" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>2</v>
       </c>
@@ -13210,19 +11926,16 @@
         <v>1</v>
       </c>
       <c r="AD125" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE125" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF125">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>156</v>
-      </c>
+    <row r="126" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>3</v>
       </c>
@@ -13305,19 +12018,16 @@
         <v>1</v>
       </c>
       <c r="AD126" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE126" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF126">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>157</v>
-      </c>
+    <row r="127" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>10</v>
       </c>
@@ -13403,19 +12113,16 @@
         <v>1</v>
       </c>
       <c r="AD127" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE127" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF127">
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>158</v>
-      </c>
+    <row r="128" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>3</v>
       </c>
@@ -13474,19 +12181,16 @@
         <v>1</v>
       </c>
       <c r="AD128" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE128" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF128">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>159</v>
-      </c>
+    <row r="129" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>10</v>
       </c>
@@ -13554,19 +12258,16 @@
         <v>1</v>
       </c>
       <c r="AD129" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE129" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF129">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>160</v>
-      </c>
+    <row r="130" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>10</v>
       </c>
@@ -13652,19 +12353,16 @@
         <v>1</v>
       </c>
       <c r="AD130" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE130" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF130">
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>161</v>
-      </c>
+    <row r="131" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>4</v>
       </c>
@@ -13750,19 +12448,16 @@
         <v>1</v>
       </c>
       <c r="AD131" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE131" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF131">
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>162</v>
-      </c>
+    <row r="132" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>6</v>
       </c>
@@ -13848,19 +12543,16 @@
         <v>2</v>
       </c>
       <c r="AD132" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE132" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF132">
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>163</v>
-      </c>
+    <row r="133" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>10</v>
       </c>
@@ -13946,19 +12638,16 @@
         <v>2</v>
       </c>
       <c r="AD133" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE133" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF133">
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>164</v>
-      </c>
+    <row r="134" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>2.5</v>
       </c>
@@ -14035,19 +12724,16 @@
         <v>2</v>
       </c>
       <c r="AD134" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE134" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF134">
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>165</v>
-      </c>
+    <row r="135" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>7.25</v>
       </c>
@@ -14133,19 +12819,16 @@
         <v>4</v>
       </c>
       <c r="AD135" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE135" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF135">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>166</v>
-      </c>
+    <row r="136" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>4</v>
       </c>
@@ -14231,19 +12914,16 @@
         <v>1</v>
       </c>
       <c r="AD136" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE136" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF136">
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>167</v>
-      </c>
+    <row r="137" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>3</v>
       </c>
@@ -14329,19 +13009,16 @@
         <v>1</v>
       </c>
       <c r="AD137" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE137" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF137">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>168</v>
-      </c>
+    <row r="138" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>3</v>
       </c>
@@ -14409,19 +13086,16 @@
         <v>2</v>
       </c>
       <c r="AD138" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE138" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF138">
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>169</v>
-      </c>
+    <row r="139" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>10</v>
       </c>
@@ -14507,19 +13181,16 @@
         <v>1</v>
       </c>
       <c r="AD139" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE139" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF139">
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>170</v>
-      </c>
+    <row r="140" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>10</v>
       </c>
@@ -14605,19 +13276,16 @@
         <v>1</v>
       </c>
       <c r="AD140" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE140" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF140">
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>171</v>
-      </c>
+    <row r="141" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>6</v>
       </c>
@@ -14694,19 +13362,16 @@
         <v>1</v>
       </c>
       <c r="AD141" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE141" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF141">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>172</v>
-      </c>
+    <row r="142" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B142">
         <v>10</v>
       </c>
@@ -14792,19 +13457,16 @@
         <v>1</v>
       </c>
       <c r="AD142" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE142" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF142">
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>173</v>
-      </c>
+    <row r="143" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>10</v>
       </c>
@@ -14890,19 +13552,16 @@
         <v>1</v>
       </c>
       <c r="AD143" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE143" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF143">
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>174</v>
-      </c>
+    <row r="144" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>6</v>
       </c>
@@ -14988,19 +13647,16 @@
         <v>1</v>
       </c>
       <c r="AD144" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE144" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF144">
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>175</v>
-      </c>
+    <row r="145" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>1</v>
       </c>
@@ -15068,19 +13724,16 @@
         <v>2</v>
       </c>
       <c r="AD145" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE145" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF145">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>176</v>
-      </c>
+    <row r="146" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>9</v>
       </c>
@@ -15166,19 +13819,16 @@
         <v>1</v>
       </c>
       <c r="AD146" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE146" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF146">
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>177</v>
-      </c>
+    <row r="147" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>10</v>
       </c>
@@ -15264,19 +13914,16 @@
         <v>1</v>
       </c>
       <c r="AD147" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE147" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF147">
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>178</v>
-      </c>
+    <row r="148" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>8</v>
       </c>
@@ -15353,19 +14000,16 @@
         <v>1</v>
       </c>
       <c r="AD148" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE148" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF148">
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>179</v>
-      </c>
+    <row r="149" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>0</v>
       </c>
@@ -15415,19 +14059,16 @@
         <v>1</v>
       </c>
       <c r="AD149" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE149" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF149">
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>180</v>
-      </c>
+    <row r="150" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>10</v>
       </c>
@@ -15513,19 +14154,16 @@
         <v>1</v>
       </c>
       <c r="AD150" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE150" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF150">
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>181</v>
-      </c>
+    <row r="151" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>10</v>
       </c>
@@ -15611,19 +14249,16 @@
         <v>1</v>
       </c>
       <c r="AD151" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE151" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF151">
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>182</v>
-      </c>
+    <row r="152" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>10</v>
       </c>
@@ -15709,19 +14344,16 @@
         <v>1</v>
       </c>
       <c r="AD152" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE152" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF152">
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>183</v>
-      </c>
+    <row r="153" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>10</v>
       </c>
@@ -15807,19 +14439,16 @@
         <v>1</v>
       </c>
       <c r="AD153" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE153" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF153">
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>184</v>
-      </c>
+    <row r="154" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>7</v>
       </c>
@@ -15896,19 +14525,16 @@
         <v>1</v>
       </c>
       <c r="AD154" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE154" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF154">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>185</v>
-      </c>
+    <row r="155" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>8</v>
       </c>
@@ -15994,19 +14620,16 @@
         <v>1</v>
       </c>
       <c r="AD155" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE155" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF155">
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>186</v>
-      </c>
+    <row r="156" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>3</v>
       </c>
@@ -16092,19 +14715,16 @@
         <v>2</v>
       </c>
       <c r="AD156" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE156" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF156">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>187</v>
-      </c>
+    <row r="157" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>5</v>
       </c>
@@ -16190,19 +14810,16 @@
         <v>1</v>
       </c>
       <c r="AD157" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE157" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF157">
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>188</v>
-      </c>
+    <row r="158" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>9</v>
       </c>
@@ -16288,19 +14905,16 @@
         <v>2</v>
       </c>
       <c r="AD158" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE158" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF158">
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>189</v>
-      </c>
+    <row r="159" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>1.666666666666667</v>
       </c>
@@ -16386,19 +15000,16 @@
         <v>3</v>
       </c>
       <c r="AD159" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE159" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF159">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>190</v>
-      </c>
+    <row r="160" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>10</v>
       </c>
@@ -16484,19 +15095,16 @@
         <v>1</v>
       </c>
       <c r="AD160" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE160" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF160">
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>191</v>
-      </c>
+    <row r="161" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>0</v>
       </c>
@@ -16537,19 +15145,16 @@
         <v>1</v>
       </c>
       <c r="AD161" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE161" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF161">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>192</v>
-      </c>
+    <row r="162" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>6</v>
       </c>
@@ -16626,19 +15231,16 @@
         <v>1</v>
       </c>
       <c r="AD162" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE162" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF162">
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>193</v>
-      </c>
+    <row r="163" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>10</v>
       </c>
@@ -16724,19 +15326,16 @@
         <v>2</v>
       </c>
       <c r="AD163" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE163" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF163">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>194</v>
-      </c>
+    <row r="164" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>10</v>
       </c>
@@ -16822,19 +15421,16 @@
         <v>2</v>
       </c>
       <c r="AD164" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE164" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF164">
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>195</v>
-      </c>
+    <row r="165" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>2</v>
       </c>
@@ -16920,19 +15516,16 @@
         <v>1</v>
       </c>
       <c r="AD165" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE165" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF165">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>196</v>
-      </c>
+    <row r="166" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>5</v>
       </c>
@@ -17018,19 +15611,16 @@
         <v>3</v>
       </c>
       <c r="AD166" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE166" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF166">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>197</v>
-      </c>
+    <row r="167" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>9</v>
       </c>
@@ -17116,19 +15706,16 @@
         <v>1</v>
       </c>
       <c r="AD167" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE167" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF167">
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>198</v>
-      </c>
+    <row r="168" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>5</v>
       </c>
@@ -17214,19 +15801,16 @@
         <v>1</v>
       </c>
       <c r="AD168" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE168" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF168">
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>199</v>
-      </c>
+    <row r="169" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>4</v>
       </c>
@@ -17312,19 +15896,16 @@
         <v>1</v>
       </c>
       <c r="AD169" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE169" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF169">
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>200</v>
-      </c>
+    <row r="170" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>10</v>
       </c>
@@ -17410,19 +15991,16 @@
         <v>1</v>
       </c>
       <c r="AD170" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE170" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF170">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>201</v>
-      </c>
+    <row r="171" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>0</v>
       </c>
@@ -17499,19 +16077,16 @@
         <v>1</v>
       </c>
       <c r="AD171" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE171" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF171">
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>202</v>
-      </c>
+    <row r="172" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>2</v>
       </c>
@@ -17597,19 +16172,16 @@
         <v>1</v>
       </c>
       <c r="AD172" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE172" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF172">
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>203</v>
-      </c>
+    <row r="173" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>10</v>
       </c>
@@ -17695,19 +16267,16 @@
         <v>1</v>
       </c>
       <c r="AD173" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE173" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF173">
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>204</v>
-      </c>
+    <row r="174" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>1</v>
       </c>
@@ -17784,19 +16353,16 @@
         <v>3</v>
       </c>
       <c r="AD174" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE174" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF174">
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>205</v>
-      </c>
+    <row r="175" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>9</v>
       </c>
@@ -17882,19 +16448,16 @@
         <v>3</v>
       </c>
       <c r="AD175" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE175" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF175">
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>206</v>
-      </c>
+    <row r="176" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>9.6666666666666661</v>
       </c>
@@ -17980,19 +16543,16 @@
         <v>3</v>
       </c>
       <c r="AD176" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE176" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF176">
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>207</v>
-      </c>
+    <row r="177" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>5</v>
       </c>
@@ -18069,19 +16629,16 @@
         <v>1</v>
       </c>
       <c r="AD177" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE177" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF177">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>208</v>
-      </c>
+    <row r="178" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>10</v>
       </c>
@@ -18167,19 +16724,16 @@
         <v>3</v>
       </c>
       <c r="AD178" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE178" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF178">
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>209</v>
-      </c>
+    <row r="179" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>10</v>
       </c>
@@ -18265,19 +16819,16 @@
         <v>2</v>
       </c>
       <c r="AD179" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE179" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF179">
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>210</v>
-      </c>
+    <row r="180" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>8</v>
       </c>
@@ -18363,19 +16914,16 @@
         <v>1</v>
       </c>
       <c r="AD180" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE180" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF180">
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>211</v>
-      </c>
+    <row r="181" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>4</v>
       </c>
@@ -18461,19 +17009,16 @@
         <v>2</v>
       </c>
       <c r="AD181" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE181" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF181">
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>212</v>
-      </c>
+    <row r="182" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B182">
         <v>10</v>
       </c>
@@ -18559,19 +17104,16 @@
         <v>1</v>
       </c>
       <c r="AD182" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE182" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF182">
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>213</v>
-      </c>
+    <row r="183" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B183">
         <v>10</v>
       </c>
@@ -18657,19 +17199,16 @@
         <v>1</v>
       </c>
       <c r="AD183" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE183" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF183">
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
-        <v>214</v>
-      </c>
+    <row r="184" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>10</v>
       </c>
@@ -18746,19 +17285,16 @@
         <v>1</v>
       </c>
       <c r="AD184" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE184" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF184">
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>215</v>
-      </c>
+    <row r="185" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B185">
         <v>10</v>
       </c>
@@ -18844,19 +17380,16 @@
         <v>1</v>
       </c>
       <c r="AD185" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE185" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF185">
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>216</v>
-      </c>
+    <row r="186" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B186">
         <v>10</v>
       </c>
@@ -18942,19 +17475,16 @@
         <v>1</v>
       </c>
       <c r="AD186" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE186" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF186">
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>217</v>
-      </c>
+    <row r="187" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B187">
         <v>6</v>
       </c>
@@ -19040,19 +17570,16 @@
         <v>1</v>
       </c>
       <c r="AD187" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE187" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF187">
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
-        <v>218</v>
-      </c>
+    <row r="188" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B188">
         <v>6.5</v>
       </c>
@@ -19138,19 +17665,16 @@
         <v>2</v>
       </c>
       <c r="AD188" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE188" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF188">
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>219</v>
-      </c>
+    <row r="189" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>6</v>
       </c>
@@ -19236,19 +17760,16 @@
         <v>1</v>
       </c>
       <c r="AD189" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE189" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF189">
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
-        <v>220</v>
-      </c>
+    <row r="190" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B190">
         <v>6</v>
       </c>
@@ -19322,19 +17843,16 @@
         <v>1</v>
       </c>
       <c r="AD190" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE190" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF190">
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
-        <v>221</v>
-      </c>
+    <row r="191" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B191">
         <v>5</v>
       </c>
@@ -19420,19 +17938,16 @@
         <v>2</v>
       </c>
       <c r="AD191" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE191" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF191">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>222</v>
-      </c>
+    <row r="192" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B192">
         <v>10</v>
       </c>
@@ -19518,19 +18033,16 @@
         <v>1</v>
       </c>
       <c r="AD192" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE192" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF192">
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>223</v>
-      </c>
+    <row r="193" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>8</v>
       </c>
@@ -19616,19 +18128,16 @@
         <v>3</v>
       </c>
       <c r="AD193" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE193" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF193">
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
-        <v>224</v>
-      </c>
+    <row r="194" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>4</v>
       </c>
@@ -19714,19 +18223,16 @@
         <v>2</v>
       </c>
       <c r="AD194" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE194" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF194">
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
-        <v>225</v>
-      </c>
+    <row r="195" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B195">
         <v>10</v>
       </c>
@@ -19812,19 +18318,16 @@
         <v>2</v>
       </c>
       <c r="AD195" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE195" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF195">
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>226</v>
-      </c>
+    <row r="196" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B196">
         <v>3</v>
       </c>
@@ -19910,19 +18413,16 @@
         <v>1</v>
       </c>
       <c r="AD196" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE196" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF196">
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>227</v>
-      </c>
+    <row r="197" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B197">
         <v>9</v>
       </c>
@@ -20008,19 +18508,16 @@
         <v>2</v>
       </c>
       <c r="AD197" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE197" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF197">
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>228</v>
-      </c>
+    <row r="198" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>4</v>
       </c>
@@ -20097,19 +18594,16 @@
         <v>1</v>
       </c>
       <c r="AD198" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE198" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF198">
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>229</v>
-      </c>
+    <row r="199" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>2</v>
       </c>
@@ -20177,19 +18671,16 @@
         <v>1</v>
       </c>
       <c r="AD199" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE199" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF199">
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>230</v>
-      </c>
+    <row r="200" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B200">
         <v>4</v>
       </c>
@@ -20275,19 +18766,16 @@
         <v>1</v>
       </c>
       <c r="AD200" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE200" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF200">
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>231</v>
-      </c>
+    <row r="201" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B201">
         <v>6</v>
       </c>
@@ -20373,19 +18861,16 @@
         <v>1</v>
       </c>
       <c r="AD201" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE201" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF201">
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>232</v>
-      </c>
+    <row r="202" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>0</v>
       </c>
@@ -20435,19 +18920,16 @@
         <v>1</v>
       </c>
       <c r="AD202" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE202" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF202">
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>233</v>
-      </c>
+    <row r="203" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B203">
         <v>5</v>
       </c>
@@ -20506,19 +18988,16 @@
         <v>1</v>
       </c>
       <c r="AD203" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE203" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF203">
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>234</v>
-      </c>
+    <row r="204" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B204">
         <v>0</v>
       </c>
@@ -20577,19 +19056,16 @@
         <v>1</v>
       </c>
       <c r="AD204" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE204" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF204">
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>235</v>
-      </c>
+    <row r="205" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B205">
         <v>6</v>
       </c>
@@ -20675,19 +19151,16 @@
         <v>1</v>
       </c>
       <c r="AD205" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE205" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF205">
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>236</v>
-      </c>
+    <row r="206" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B206">
         <v>10</v>
       </c>
@@ -20764,19 +19237,16 @@
         <v>1</v>
       </c>
       <c r="AD206" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE206" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF206">
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>237</v>
-      </c>
+    <row r="207" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B207">
         <v>10</v>
       </c>
@@ -20862,19 +19332,16 @@
         <v>1</v>
       </c>
       <c r="AD207" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE207" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF207">
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>238</v>
-      </c>
+    <row r="208" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B208">
         <v>2</v>
       </c>
@@ -20951,19 +19418,16 @@
         <v>1</v>
       </c>
       <c r="AD208" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE208" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF208">
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>239</v>
-      </c>
+    <row r="209" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B209">
         <v>3</v>
       </c>
@@ -21031,19 +19495,16 @@
         <v>1</v>
       </c>
       <c r="AD209" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE209" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF209">
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>240</v>
-      </c>
+    <row r="210" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B210">
         <v>2</v>
       </c>
@@ -21120,19 +19581,16 @@
         <v>1</v>
       </c>
       <c r="AD210" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE210" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF210">
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>241</v>
-      </c>
+    <row r="211" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B211">
         <v>10</v>
       </c>
@@ -21218,19 +19676,16 @@
         <v>1</v>
       </c>
       <c r="AD211" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE211" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF211">
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>242</v>
-      </c>
+    <row r="212" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B212">
         <v>0</v>
       </c>
@@ -21307,19 +19762,16 @@
         <v>1</v>
       </c>
       <c r="AD212" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE212" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF212">
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>243</v>
-      </c>
+    <row r="213" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B213">
         <v>3</v>
       </c>
@@ -21405,19 +19857,16 @@
         <v>1</v>
       </c>
       <c r="AD213" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE213" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF213">
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>244</v>
-      </c>
+    <row r="214" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B214">
         <v>2</v>
       </c>
@@ -21485,19 +19934,16 @@
         <v>1</v>
       </c>
       <c r="AD214" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE214" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF214">
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>245</v>
-      </c>
+    <row r="215" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B215">
         <v>10</v>
       </c>
@@ -21583,19 +20029,16 @@
         <v>1</v>
       </c>
       <c r="AD215" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE215" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF215">
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
-        <v>246</v>
-      </c>
+    <row r="216" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B216">
         <v>4</v>
       </c>
@@ -21672,19 +20115,16 @@
         <v>1</v>
       </c>
       <c r="AD216" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE216" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF216">
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
-        <v>247</v>
-      </c>
+    <row r="217" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B217">
         <v>5</v>
       </c>
@@ -21770,19 +20210,16 @@
         <v>1</v>
       </c>
       <c r="AD217" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE217" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF217">
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A218" t="s">
-        <v>248</v>
-      </c>
+    <row r="218" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B218">
         <v>8</v>
       </c>
@@ -21856,19 +20293,16 @@
         <v>1</v>
       </c>
       <c r="AD218" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE218" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF218">
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A219" t="s">
-        <v>249</v>
-      </c>
+    <row r="219" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B219">
         <v>4</v>
       </c>
@@ -21954,19 +20388,16 @@
         <v>1</v>
       </c>
       <c r="AD219" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE219" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF219">
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
-        <v>250</v>
-      </c>
+    <row r="220" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B220">
         <v>2.5</v>
       </c>
@@ -22052,19 +20483,16 @@
         <v>2</v>
       </c>
       <c r="AD220" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE220" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF220">
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
-        <v>251</v>
-      </c>
+    <row r="221" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B221">
         <v>10</v>
       </c>
@@ -22150,19 +20578,16 @@
         <v>1</v>
       </c>
       <c r="AD221" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE221" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF221">
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
-        <v>252</v>
-      </c>
+    <row r="222" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B222">
         <v>5</v>
       </c>
@@ -22248,19 +20673,16 @@
         <v>1</v>
       </c>
       <c r="AD222" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE222" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF222">
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A223" t="s">
-        <v>253</v>
-      </c>
+    <row r="223" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B223">
         <v>6</v>
       </c>
@@ -22346,19 +20768,16 @@
         <v>1</v>
       </c>
       <c r="AD223" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE223" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF223">
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>254</v>
-      </c>
+    <row r="224" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B224">
         <v>5</v>
       </c>
@@ -22444,19 +20863,16 @@
         <v>1</v>
       </c>
       <c r="AD224" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE224" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF224">
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
-        <v>255</v>
-      </c>
+    <row r="225" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B225">
         <v>6</v>
       </c>
@@ -22542,19 +20958,16 @@
         <v>1</v>
       </c>
       <c r="AD225" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE225" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF225">
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
-        <v>256</v>
-      </c>
+    <row r="226" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B226">
         <v>7</v>
       </c>
@@ -22640,19 +21053,16 @@
         <v>1</v>
       </c>
       <c r="AD226" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE226" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF226">
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
-        <v>257</v>
-      </c>
+    <row r="227" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B227">
         <v>9.3333333333333339</v>
       </c>
@@ -22738,19 +21148,16 @@
         <v>3</v>
       </c>
       <c r="AD227" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE227" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF227">
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
-        <v>258</v>
-      </c>
+    <row r="228" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B228">
         <v>10</v>
       </c>
@@ -22836,19 +21243,16 @@
         <v>1</v>
       </c>
       <c r="AD228" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE228" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF228">
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>259</v>
-      </c>
+    <row r="229" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B229">
         <v>7</v>
       </c>
@@ -22934,19 +21338,16 @@
         <v>3</v>
       </c>
       <c r="AD229" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE229" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF229">
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A230" t="s">
-        <v>260</v>
-      </c>
+    <row r="230" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B230">
         <v>3</v>
       </c>
@@ -23014,19 +21415,16 @@
         <v>1</v>
       </c>
       <c r="AD230" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE230" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF230">
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
-        <v>261</v>
-      </c>
+    <row r="231" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B231">
         <v>6</v>
       </c>
@@ -23112,19 +21510,16 @@
         <v>1</v>
       </c>
       <c r="AD231" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE231" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF231">
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>262</v>
-      </c>
+    <row r="232" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B232">
         <v>10</v>
       </c>
@@ -23210,19 +21605,16 @@
         <v>1</v>
       </c>
       <c r="AD232" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE232" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF232">
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
-        <v>263</v>
-      </c>
+    <row r="233" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B233">
         <v>5</v>
       </c>
@@ -23308,19 +21700,16 @@
         <v>1</v>
       </c>
       <c r="AD233" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE233" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF233">
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
-        <v>264</v>
-      </c>
+    <row r="234" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B234">
         <v>5</v>
       </c>
@@ -23406,19 +21795,16 @@
         <v>1</v>
       </c>
       <c r="AD234" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE234" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF234">
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
-        <v>265</v>
-      </c>
+    <row r="235" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B235">
         <v>5</v>
       </c>
@@ -23495,19 +21881,16 @@
         <v>1</v>
       </c>
       <c r="AD235" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE235" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF235">
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
-        <v>266</v>
-      </c>
+    <row r="236" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B236">
         <v>6</v>
       </c>
@@ -23593,19 +21976,16 @@
         <v>1</v>
       </c>
       <c r="AD236" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE236" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF236">
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
-        <v>267</v>
-      </c>
+    <row r="237" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B237">
         <v>6</v>
       </c>
@@ -23691,19 +22071,16 @@
         <v>1</v>
       </c>
       <c r="AD237" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE237" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF237">
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
-        <v>268</v>
-      </c>
+    <row r="238" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B238">
         <v>10</v>
       </c>
@@ -23789,19 +22166,16 @@
         <v>1</v>
       </c>
       <c r="AD238" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE238" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF238">
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
-        <v>269</v>
-      </c>
+    <row r="239" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B239">
         <v>2</v>
       </c>
@@ -23872,19 +22246,16 @@
         <v>1</v>
       </c>
       <c r="AD239" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE239" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF239">
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
-        <v>270</v>
-      </c>
+    <row r="240" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B240">
         <v>4</v>
       </c>
@@ -23970,19 +22341,16 @@
         <v>1</v>
       </c>
       <c r="AD240" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE240" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF240">
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
-        <v>271</v>
-      </c>
+    <row r="241" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B241">
         <v>1</v>
       </c>
@@ -24038,19 +22406,16 @@
         <v>1</v>
       </c>
       <c r="AD241" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE241" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF241">
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
-        <v>272</v>
-      </c>
+    <row r="242" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B242">
         <v>7</v>
       </c>
@@ -24136,19 +22501,16 @@
         <v>1</v>
       </c>
       <c r="AD242" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE242" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF242">
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
-        <v>273</v>
-      </c>
+    <row r="243" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B243">
         <v>10</v>
       </c>
@@ -24234,19 +22596,16 @@
         <v>2</v>
       </c>
       <c r="AD243" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE243" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF243">
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
-        <v>274</v>
-      </c>
+    <row r="244" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B244">
         <v>10</v>
       </c>
@@ -24332,19 +22691,16 @@
         <v>2</v>
       </c>
       <c r="AD244" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE244" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF244">
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A245" t="s">
-        <v>275</v>
-      </c>
+    <row r="245" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B245">
         <v>7</v>
       </c>
@@ -24412,19 +22768,16 @@
         <v>1</v>
       </c>
       <c r="AD245" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE245" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF245">
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
-        <v>276</v>
-      </c>
+    <row r="246" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B246">
         <v>1</v>
       </c>
@@ -24483,19 +22836,16 @@
         <v>1</v>
       </c>
       <c r="AD246" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE246" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF246">
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
-        <v>277</v>
-      </c>
+    <row r="247" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B247">
         <v>8.6666666666666661</v>
       </c>
@@ -24581,19 +22931,16 @@
         <v>3</v>
       </c>
       <c r="AD247" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE247" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF247">
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
-        <v>278</v>
-      </c>
+    <row r="248" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B248">
         <v>6</v>
       </c>
@@ -24679,19 +23026,16 @@
         <v>1</v>
       </c>
       <c r="AD248" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE248" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF248">
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>279</v>
-      </c>
+    <row r="249" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B249">
         <v>10</v>
       </c>
@@ -24777,19 +23121,16 @@
         <v>1</v>
       </c>
       <c r="AD249" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE249" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF249">
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
-        <v>280</v>
-      </c>
+    <row r="250" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B250">
         <v>10</v>
       </c>
@@ -24875,19 +23216,16 @@
         <v>1</v>
       </c>
       <c r="AD250" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE250" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF250">
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A251" t="s">
-        <v>281</v>
-      </c>
+    <row r="251" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B251">
         <v>3</v>
       </c>
@@ -24973,19 +23311,16 @@
         <v>1</v>
       </c>
       <c r="AD251" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE251" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF251">
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A252" t="s">
-        <v>282</v>
-      </c>
+    <row r="252" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B252">
         <v>2</v>
       </c>
@@ -25044,19 +23379,16 @@
         <v>1</v>
       </c>
       <c r="AD252" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE252" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF252">
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
-        <v>283</v>
-      </c>
+    <row r="253" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B253">
         <v>10</v>
       </c>
@@ -25142,19 +23474,16 @@
         <v>1</v>
       </c>
       <c r="AD253" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE253" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF253">
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A254" t="s">
-        <v>284</v>
-      </c>
+    <row r="254" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B254">
         <v>6</v>
       </c>
@@ -25219,19 +23548,16 @@
         <v>1</v>
       </c>
       <c r="AD254" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE254" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF254">
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
-        <v>285</v>
-      </c>
+    <row r="255" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B255">
         <v>10</v>
       </c>
@@ -25317,19 +23643,16 @@
         <v>1</v>
       </c>
       <c r="AD255" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE255" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF255">
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>286</v>
-      </c>
+    <row r="256" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B256">
         <v>8</v>
       </c>
@@ -25415,19 +23738,16 @@
         <v>1</v>
       </c>
       <c r="AD256" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE256" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF256">
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
-        <v>287</v>
-      </c>
+    <row r="257" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B257">
         <v>6</v>
       </c>
@@ -25513,19 +23833,16 @@
         <v>1</v>
       </c>
       <c r="AD257" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE257" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF257">
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A258" t="s">
-        <v>288</v>
-      </c>
+    <row r="258" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B258">
         <v>7</v>
       </c>
@@ -25602,19 +23919,16 @@
         <v>1</v>
       </c>
       <c r="AD258" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE258" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF258">
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A259" t="s">
-        <v>289</v>
-      </c>
+    <row r="259" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B259">
         <v>0</v>
       </c>
@@ -25673,19 +23987,16 @@
         <v>1</v>
       </c>
       <c r="AD259" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE259" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF259">
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A260" t="s">
-        <v>290</v>
-      </c>
+    <row r="260" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B260">
         <v>10</v>
       </c>
@@ -25744,19 +24055,16 @@
         <v>1</v>
       </c>
       <c r="AD260" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE260" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF260">
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A261" t="s">
-        <v>291</v>
-      </c>
+    <row r="261" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B261">
         <v>7</v>
       </c>
@@ -25842,19 +24150,16 @@
         <v>2</v>
       </c>
       <c r="AD261" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE261" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF261">
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A262" t="s">
-        <v>292</v>
-      </c>
+    <row r="262" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B262">
         <v>10</v>
       </c>
@@ -25940,19 +24245,16 @@
         <v>1</v>
       </c>
       <c r="AD262" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE262" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF262">
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A263" t="s">
-        <v>293</v>
-      </c>
+    <row r="263" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B263">
         <v>10</v>
       </c>
@@ -26038,19 +24340,16 @@
         <v>1</v>
       </c>
       <c r="AD263" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE263" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF263">
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A264" t="s">
-        <v>294</v>
-      </c>
+    <row r="264" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B264">
         <v>10</v>
       </c>
@@ -26136,19 +24435,16 @@
         <v>1</v>
       </c>
       <c r="AD264" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE264" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF264">
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A265" t="s">
-        <v>295</v>
-      </c>
+    <row r="265" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B265">
         <v>1.5</v>
       </c>
@@ -26225,19 +24521,16 @@
         <v>2</v>
       </c>
       <c r="AD265" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE265" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF265">
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A266" t="s">
-        <v>296</v>
-      </c>
+    <row r="266" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B266">
         <v>2</v>
       </c>
@@ -26323,19 +24616,16 @@
         <v>2</v>
       </c>
       <c r="AD266" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE266" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF266">
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A267" t="s">
-        <v>297</v>
-      </c>
+    <row r="267" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B267">
         <v>2</v>
       </c>
@@ -26412,19 +24702,16 @@
         <v>1</v>
       </c>
       <c r="AD267" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE267" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF267">
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A268" t="s">
-        <v>298</v>
-      </c>
+    <row r="268" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B268">
         <v>6</v>
       </c>
@@ -26507,19 +24794,16 @@
         <v>1</v>
       </c>
       <c r="AD268" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE268" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF268">
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A269" t="s">
-        <v>299</v>
-      </c>
+    <row r="269" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B269">
         <v>9</v>
       </c>
@@ -26605,19 +24889,16 @@
         <v>1</v>
       </c>
       <c r="AD269" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE269" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF269">
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A270" t="s">
-        <v>300</v>
-      </c>
+    <row r="270" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B270">
         <v>4</v>
       </c>
@@ -26685,19 +24966,16 @@
         <v>1</v>
       </c>
       <c r="AD270" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE270" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF270">
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
-        <v>301</v>
-      </c>
+    <row r="271" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B271">
         <v>5</v>
       </c>
@@ -26783,19 +25061,16 @@
         <v>1</v>
       </c>
       <c r="AD271" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE271" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF271">
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A272" t="s">
-        <v>302</v>
-      </c>
+    <row r="272" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B272">
         <v>10</v>
       </c>
@@ -26881,19 +25156,16 @@
         <v>1</v>
       </c>
       <c r="AD272" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE272" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF272">
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>303</v>
-      </c>
+    <row r="273" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B273">
         <v>8</v>
       </c>
@@ -26979,19 +25251,16 @@
         <v>1</v>
       </c>
       <c r="AD273" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE273" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF273">
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>304</v>
-      </c>
+    <row r="274" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B274">
         <v>6</v>
       </c>
@@ -27077,19 +25346,16 @@
         <v>1</v>
       </c>
       <c r="AD274" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE274" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF274">
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>305</v>
-      </c>
+    <row r="275" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B275">
         <v>10</v>
       </c>
@@ -27175,19 +25441,16 @@
         <v>1</v>
       </c>
       <c r="AD275" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE275" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF275">
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
-        <v>306</v>
-      </c>
+    <row r="276" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B276">
         <v>6</v>
       </c>
@@ -27273,19 +25536,16 @@
         <v>2</v>
       </c>
       <c r="AD276" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE276" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF276">
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>307</v>
-      </c>
+    <row r="277" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B277">
         <v>4</v>
       </c>
@@ -27362,19 +25622,16 @@
         <v>1</v>
       </c>
       <c r="AD277" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE277" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF277">
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
-        <v>308</v>
-      </c>
+    <row r="278" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B278">
         <v>0</v>
       </c>
@@ -27424,19 +25681,16 @@
         <v>1</v>
       </c>
       <c r="AD278" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE278" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF278">
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
-        <v>309</v>
-      </c>
+    <row r="279" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B279">
         <v>1</v>
       </c>
@@ -27504,19 +25758,16 @@
         <v>1</v>
       </c>
       <c r="AD279" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE279" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF279">
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
-        <v>310</v>
-      </c>
+    <row r="280" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B280">
         <v>2</v>
       </c>
@@ -27602,19 +25853,16 @@
         <v>1</v>
       </c>
       <c r="AD280" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE280" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF280">
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>311</v>
-      </c>
+    <row r="281" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B281">
         <v>4</v>
       </c>
@@ -27691,19 +25939,16 @@
         <v>1</v>
       </c>
       <c r="AD281" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE281" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF281">
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>312</v>
-      </c>
+    <row r="282" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B282">
         <v>10</v>
       </c>
@@ -27789,19 +26034,16 @@
         <v>1</v>
       </c>
       <c r="AD282" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE282" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF282">
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>313</v>
-      </c>
+    <row r="283" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B283">
         <v>10</v>
       </c>
@@ -27869,19 +26111,16 @@
         <v>2</v>
       </c>
       <c r="AD283" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="AE283" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF283">
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>314</v>
-      </c>
+    <row r="284" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B284">
         <v>10</v>
       </c>
@@ -27967,19 +26206,16 @@
         <v>2</v>
       </c>
       <c r="AD284" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE284" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF284">
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
-        <v>315</v>
-      </c>
+    <row r="285" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B285">
         <v>10</v>
       </c>
@@ -28065,19 +26301,16 @@
         <v>1</v>
       </c>
       <c r="AD285" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE285" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF285">
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>316</v>
-      </c>
+    <row r="286" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B286">
         <v>10</v>
       </c>
@@ -28163,19 +26396,16 @@
         <v>1</v>
       </c>
       <c r="AD286" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE286" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF286">
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
-        <v>317</v>
-      </c>
+    <row r="287" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B287">
         <v>10</v>
       </c>
@@ -28261,19 +26491,16 @@
         <v>1</v>
       </c>
       <c r="AD287" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE287" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF287">
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
-        <v>318</v>
-      </c>
+    <row r="288" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B288">
         <v>6</v>
       </c>
@@ -28341,19 +26568,16 @@
         <v>1</v>
       </c>
       <c r="AD288" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE288" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF288">
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
-        <v>319</v>
-      </c>
+    <row r="289" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B289">
         <v>10</v>
       </c>
@@ -28439,19 +26663,16 @@
         <v>1</v>
       </c>
       <c r="AD289" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE289" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF289">
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
-        <v>320</v>
-      </c>
+    <row r="290" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B290">
         <v>2</v>
       </c>
@@ -28519,19 +26740,16 @@
         <v>1</v>
       </c>
       <c r="AD290" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE290" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF290">
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>321</v>
-      </c>
+    <row r="291" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B291">
         <v>10</v>
       </c>
@@ -28617,19 +26835,16 @@
         <v>1</v>
       </c>
       <c r="AD291" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE291" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF291">
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>322</v>
-      </c>
+    <row r="292" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B292">
         <v>10</v>
       </c>
@@ -28715,19 +26930,16 @@
         <v>1</v>
       </c>
       <c r="AD292" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE292" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF292">
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>323</v>
-      </c>
+    <row r="293" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B293">
         <v>10</v>
       </c>
@@ -28810,19 +27022,16 @@
         <v>1</v>
       </c>
       <c r="AD293" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE293" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF293">
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>324</v>
-      </c>
+    <row r="294" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B294">
         <v>3</v>
       </c>
@@ -28908,19 +27117,16 @@
         <v>1</v>
       </c>
       <c r="AD294" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE294" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF294">
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>325</v>
-      </c>
+    <row r="295" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B295">
         <v>10</v>
       </c>
@@ -29003,19 +27209,16 @@
         <v>1</v>
       </c>
       <c r="AD295" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE295" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF295">
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>326</v>
-      </c>
+    <row r="296" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B296">
         <v>9</v>
       </c>
@@ -29101,19 +27304,16 @@
         <v>1</v>
       </c>
       <c r="AD296" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE296" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF296">
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>327</v>
-      </c>
+    <row r="297" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B297">
         <v>10</v>
       </c>
@@ -29199,19 +27399,16 @@
         <v>1</v>
       </c>
       <c r="AD297" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE297" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF297">
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>328</v>
-      </c>
+    <row r="298" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B298">
         <v>8</v>
       </c>
@@ -29297,19 +27494,16 @@
         <v>2</v>
       </c>
       <c r="AD298" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE298" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF298">
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
-        <v>329</v>
-      </c>
+    <row r="299" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B299">
         <v>3</v>
       </c>
@@ -29395,19 +27589,16 @@
         <v>2</v>
       </c>
       <c r="AD299" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE299" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF299">
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A300" t="s">
-        <v>330</v>
-      </c>
+    <row r="300" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B300">
         <v>1</v>
       </c>
@@ -29484,19 +27675,16 @@
         <v>1</v>
       </c>
       <c r="AD300" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE300" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF300">
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A301" t="s">
-        <v>331</v>
-      </c>
+    <row r="301" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B301">
         <v>6</v>
       </c>
@@ -29582,19 +27770,16 @@
         <v>1</v>
       </c>
       <c r="AD301" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE301" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF301">
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>332</v>
-      </c>
+    <row r="302" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B302">
         <v>6.5</v>
       </c>
@@ -29680,19 +27865,16 @@
         <v>2</v>
       </c>
       <c r="AD302" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE302" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF302">
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
-        <v>333</v>
-      </c>
+    <row r="303" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B303">
         <v>9</v>
       </c>
@@ -29778,19 +27960,16 @@
         <v>1</v>
       </c>
       <c r="AD303" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE303" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="AF303">
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>334</v>
-      </c>
+    <row r="304" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B304">
         <v>10</v>
       </c>
@@ -29876,19 +28055,16 @@
         <v>1</v>
       </c>
       <c r="AD304" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="AE304" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="AF304">
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
-        <v>335</v>
-      </c>
+    <row r="305" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B305">
         <v>2</v>
       </c>
@@ -29944,10 +28120,10 @@
         <v>1</v>
       </c>
       <c r="AD305" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="AE305" t="s">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="AF305">
         <v>0</v>
